--- a/Prototype/BOM/BOM.xlsx
+++ b/Prototype/BOM/BOM.xlsx
@@ -53,7 +53,7 @@
     <t>LED</t>
   </si>
   <si>
-    <t>Botland_LED</t>
+    <t>Allegro_LED</t>
   </si>
   <si>
     <t>Switch</t>
@@ -66,11 +66,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+  <numFmts count="5">
+    <numFmt numFmtId="26" formatCode="General"/>
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -542,162 +543,165 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="26" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="26" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="26" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="26" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="26" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="26" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="26" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="26" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="26" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="26" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="26" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="26" fontId="9" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="26" fontId="10" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="26" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="26" fontId="12" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="26" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="26" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="26" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="26" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="26" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="26" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="26" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="26" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="26" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="26" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="26" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="26" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="26" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="26" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="26" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="26" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="26" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="26" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="26" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="26" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="26" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="26" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="26" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="26" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="26" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="26" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="26" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="26" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="26" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="6" applyBorder="1">
+  <cellXfs count="4">
+    <xf numFmtId="26" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="26" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="26" fontId="1" fillId="0" borderId="1" xfId="6" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="26" fontId="1" fillId="0" borderId="0" xfId="6">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1269,11 +1273,11 @@
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C4" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1292,7 +1296,7 @@
     <hyperlink ref="B2" r:id="rId1" display="Botland_Lipol"/>
     <hyperlink ref="B5" r:id="rId2" display="Botland_switch"/>
     <hyperlink ref="B3" r:id="rId3" display="Botland_TP4056"/>
-    <hyperlink ref="B4" r:id="rId4" display="Botland_LED"/>
+    <hyperlink ref="B4" r:id="rId4" display="Allegro_LED"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
